--- a/vaccine_campaign_template.xlsx
+++ b/vaccine_campaign_template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\odb\blood_test\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\odb\vaccination\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6B2838E-EDB1-4A19-B695-1D3A522B63B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13D78425-5A4B-4FE9-BB18-D5C3499240A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9252" yWindow="3756" windowWidth="16056" windowHeight="7764" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="37650" yWindow="6450" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>Date</t>
   </si>
@@ -37,18 +37,30 @@
   </si>
   <si>
     <t>&lt;--Please do not delete this row</t>
+  </si>
+  <si>
+    <t>Acknowledge</t>
+  </si>
+  <si>
+    <t>Carepro Mobile Clinic</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -69,10 +81,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -80,9 +93,13 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{5BDFA75A-C69A-4B29-8BF3-EBB6E148624C}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -360,29 +377,36 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
+      <c r="C1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="3"/>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>45954</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>3</v>
       </c>
     </row>
